--- a/Образец данных.xlsx
+++ b/Образец данных.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0c84e2eb05e56316/Projects/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC1048F3D9DE67D45BDE5902" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A64EFE4A-4199-4329-9EF4-7A21F684CD92}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_F25DC773A252ABDACC1048F3D9DE67D45BDE5902" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E771C1E7-2F32-4C49-89F1-C303AFEE1CE4}"/>
   <bookViews>
-    <workbookView xWindow="11350" yWindow="1180" windowWidth="15790" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5270" yWindow="760" windowWidth="21870" windowHeight="16520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -197,7 +197,7 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment textRotation="90"/>
     </xf>
@@ -278,237 +278,6 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SQ</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
@@ -1429,2448 +1198,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Type2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$2:$G$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="7"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Active2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$H$2:$H$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="8"/>
-          <c:order val="8"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$I$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Т2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$31</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>25.1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>25.1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="9"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$J$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Н2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$J$2:$J$31</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>62.1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>62.1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="10"/>
-          <c:order val="10"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$K$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Type3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$K$2:$K$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000A-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="11"/>
-          <c:order val="11"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Active3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$L$2:$L$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="12"/>
-          <c:order val="12"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$M$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Т3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$M$2:$M$31</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>23.4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="13"/>
-          <c:order val="13"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$N$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Н3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$N$2:$N$31</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>59</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000D-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="14"/>
-          <c:order val="14"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$O$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Type4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$O$2:$O$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="15"/>
-          <c:order val="15"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$P$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Active4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$P$2:$P$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000F-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="16"/>
-          <c:order val="16"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$Q$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Т4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$Q$2:$Q$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000010-EFCC-4C19-8C4D-F6D409343997}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="17"/>
-          <c:order val="17"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$R$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Н4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$R$2:$R$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000011-EFCC-4C19-8C4D-F6D409343997}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5280,6 +2607,2939 @@
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000000-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>SQ</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$B$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>6</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$G$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Type2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$G$2:$G$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000006-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$H$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Active2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$H$2:$H$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="8"/>
+                <c:order val="8"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$I$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Т2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$I$2:$I$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>25.1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000008-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="9"/>
+                <c:order val="9"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$J$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Н2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$J$2:$J$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>62.1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000009-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="10"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$K$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Type3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$K$2:$K$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000A-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="11"/>
+                <c:order val="11"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$L$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Active3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$L$2:$L$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000B-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="12"/>
+                <c:order val="12"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$M$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Т3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$M$2:$M$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>23.4</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000C-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="13"/>
+                <c:order val="13"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$N$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Н3</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$N$2:$N$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>59</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>59</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000D-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="14"/>
+                <c:order val="14"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$O$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Type4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$O$2:$O$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000E-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="15"/>
+                <c:order val="15"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$P$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Active4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$P$2:$P$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000F-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="16"/>
+                <c:order val="16"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Q$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Т4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$Q$2:$Q$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000010-EFCC-4C19-8C4D-F6D409343997}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="17"/>
+                <c:order val="17"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$R$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Н4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6">
+                        <a:lumMod val="80000"/>
+                        <a:lumOff val="20000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$2:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$R$2:$R$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="30"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000011-EFCC-4C19-8C4D-F6D409343997}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -6040,7 +6300,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305000" cy="6075000"/>
+    <xdr:ext cx="9300000" cy="6070000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Диаграмма 1">
@@ -6067,6 +6327,10 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
